--- a/SGC-CKN/Excel/ff98b803-fe7c-42fd-afbe-ab6d154ccb94_P11-123_P11-123_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/ff98b803-fe7c-42fd-afbe-ab6d154ccb94_P11-123_P11-123_D800_25-03-2026.xlsx
@@ -1152,7 +1152,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="5">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="5">
         <v>-3.2</v>
@@ -1161,10 +1161,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J11" s="8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1295,7 +1295,7 @@
         <v>-28.3</v>
       </c>
       <c r="G15" s="19">
-        <v>-35.4</v>
+        <v>-35.400000000000006</v>
       </c>
       <c r="H15" s="19">
         <v>0.5</v>
@@ -1327,7 +1327,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="22">
-        <v>-35.4</v>
+        <v>-35.400000000000006</v>
       </c>
       <c r="G16" s="22">
         <v>-38.2</v>
@@ -1564,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="F2" s="5">
         <v>-3.2</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I2" s="8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1796,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="F10" s="33">
         <v>-49.72</v>
@@ -1805,10 +1805,10 @@
         <v>7.22</v>
       </c>
       <c r="H10" s="33">
-        <v>48.6</v>
+        <v>48.62</v>
       </c>
       <c r="I10" s="33">
-        <v>6.73</v>
+        <v>6.74</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/ff98b803-fe7c-42fd-afbe-ab6d154ccb94_P11-123_P11-123_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/ff98b803-fe7c-42fd-afbe-ab6d154ccb94_P11-123_P11-123_D800_25-03-2026.xlsx
@@ -92,7 +92,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">20:30
@@ -109,7 +109,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">22:00
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">22:30
@@ -129,7 +129,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">23:00
@@ -153,7 +153,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">00:00
@@ -163,7 +163,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">02:01
@@ -176,7 +176,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:43
